--- a/tame_output/ON/bt/strategyON_20240108.xlsx
+++ b/tame_output/ON/bt/strategyON_20240108.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -615,11 +615,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1832</v>
+        <v>1833</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-01-06</t>
+          <t>2024-01-07</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>3.0%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>79.2%</t>
+          <t>78.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1832</v>
+        <v>1833</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-01-06</t>
+          <t>2024-01-07</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>0.2%</t>
         </is>
       </c>
     </row>
@@ -931,11 +931,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1832</v>
+        <v>1833</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-01-06</t>
+          <t>2024-01-07</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>102.2%</t>
+          <t>101.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,16 +1084,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1832</v>
+        <v>1833</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-01-06</t>
+          <t>2024-01-07</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>97.4%</t>
+          <t>96.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.1%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1832</v>
+        <v>1833</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-01-06</t>
+          <t>2024-01-07</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-155.8%</t>
+          <t>-155.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-0.6%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>131.8%</t>
+          <t>130.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,16 +1400,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1832</v>
+        <v>1833</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-01-06</t>
+          <t>2024-01-07</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>125.4%</t>
+          <t>124.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>-0.2%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1835"/>
+  <dimension ref="A1:G1836"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43750,7 +43750,7 @@
         <v>45297</v>
       </c>
       <c r="B1835" t="n">
-        <v>3.320540153593092</v>
+        <v>3.320996253831154</v>
       </c>
       <c r="C1835" t="n">
         <v>3.138175778137954</v>
@@ -43766,6 +43766,29 @@
       </c>
       <c r="G1835" t="n">
         <v>4.481165532380678</v>
+      </c>
+    </row>
+    <row r="1836">
+      <c r="A1836" s="2" t="n">
+        <v>45298</v>
+      </c>
+      <c r="B1836" t="n">
+        <v>3.310321938075317</v>
+      </c>
+      <c r="C1836" t="n">
+        <v>3.118001050765402</v>
+      </c>
+      <c r="D1836" t="n">
+        <v>1.61407550006203</v>
+      </c>
+      <c r="E1836" t="n">
+        <v>3.763274826476467</v>
+      </c>
+      <c r="F1836" t="n">
+        <v>2.233548163216526</v>
+      </c>
+      <c r="G1836" t="n">
+        <v>4.458129948695317</v>
       </c>
     </row>
   </sheetData>
